--- a/automation/reports/Excel/Vulnerability_Test_Report.xlsx
+++ b/automation/reports/Excel/Vulnerability_Test_Report.xlsx
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.257</v>
+        <v>0.118</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.301</v>
+        <v>0.151</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.342</v>
+        <v>0.138</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.149</v>
+        <v>0.349</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.199</v>
+        <v>0.313</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.265</v>
+        <v>0.278</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.339</v>
+        <v>0.104</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.337</v>
+        <v>0.192</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.201</v>
+        <v>0.264</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.194</v>
+        <v>0.239</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.383</v>
+        <v>0.195</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.28</v>
+        <v>0.213</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.229</v>
+        <v>0.368</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.128</v>
+        <v>0.309</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.395</v>
+        <v>0.149</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.111</v>
+        <v>0.162</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.099</v>
+        <v>0.164</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.179</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.177</v>
+        <v>0.396</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.09</v>
+        <v>0.408</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.326</v>
+        <v>0.264</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.376</v>
+        <v>0.245</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.203</v>
+        <v>0.154</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.091</v>
+        <v>0.378</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.326</v>
+        <v>0.386</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.373</v>
+        <v>0.261</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.336</v>
+        <v>0.358</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.279</v>
+        <v>0.14</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.408</v>
+        <v>0.219</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.131</v>
+        <v>0.201</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.157</v>
+        <v>0.116</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.169</v>
+        <v>0.172</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.123</v>
+        <v>0.3</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.345</v>
+        <v>0.41</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.389</v>
+        <v>0.17</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.126</v>
+        <v>0.089</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.221</v>
+        <v>0.303</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.331</v>
+        <v>0.322</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.337</v>
+        <v>0.206</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.125</v>
+        <v>0.234</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.36</v>
+        <v>0.106</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.287</v>
+        <v>0.411</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.14</v>
+        <v>0.238</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.259</v>
+        <v>0.189</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.09</v>
+        <v>0.325</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.244</v>
+        <v>0.124</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.194</v>
+        <v>0.124</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.35</v>
+        <v>0.188</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.345</v>
+        <v>0.147</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.39</v>
+        <v>0.307</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.282</v>
+        <v>0.297</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.396</v>
+        <v>0.223</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.189</v>
+        <v>0.313</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.224</v>
+        <v>0.229</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.101</v>
+        <v>0.42</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.131</v>
+        <v>0.183</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0.207</v>
+        <v>0.174</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.155</v>
+        <v>0.336</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.398</v>
+        <v>0.262</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.419</v>
+        <v>0.284</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.097</v>
+        <v>0.4</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.217</v>
+        <v>0.155</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.135</v>
+        <v>0.154</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.092</v>
+        <v>0.406</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.376</v>
+        <v>0.188</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>0.175</v>
+        <v>0.327</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.162</v>
+        <v>0.096</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.27</v>
+        <v>0.345</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.351</v>
+        <v>0.115</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.197</v>
+        <v>0.297</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>0.412</v>
+        <v>0.347</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>0.326</v>
+        <v>0.206</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0.206</v>
+        <v>0.324</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>0.375</v>
+        <v>0.242</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0.366</v>
+        <v>0.29</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.2</v>
+        <v>0.158</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.107</v>
+        <v>0.335</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>0.272</v>
+        <v>0.245</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.277</v>
+        <v>0.186</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0.395</v>
+        <v>0.188</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>0.35</v>
+        <v>0.112</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.15</v>
+        <v>0.224</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0.285</v>
+        <v>0.132</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0.248</v>
+        <v>0.288</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>0.226</v>
+        <v>0.244</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0.151</v>
+        <v>0.273</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0.113</v>
+        <v>0.395</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.411</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>0.265</v>
+        <v>0.396</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>0.179</v>
+        <v>0.304</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>0.328</v>
+        <v>0.216</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>0.303</v>
+        <v>0.345</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>0.121</v>
+        <v>0.081</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>0.218</v>
+        <v>0.419</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0.172</v>
+        <v>0.294</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>0.129</v>
+        <v>0.214</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>0.241</v>
+        <v>0.277</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>0.283</v>
+        <v>0.29</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.238</v>
+        <v>0.369</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0.26</v>
+        <v>0.109</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0.244</v>
+        <v>0.235</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0.31</v>
+        <v>0.109</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.294</v>
+        <v>0.108</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0.195</v>
+        <v>0.415</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>0.368</v>
+        <v>0.28</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.329</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>0.334</v>
+        <v>0.288</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>0.39</v>
+        <v>0.133</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>0.326</v>
+        <v>0.347</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0.263</v>
+        <v>0.368</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>0.34</v>
+        <v>0.232</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>0.23</v>
+        <v>0.254</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>0.207</v>
+        <v>0.296</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>0.144</v>
+        <v>0.136</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0.175</v>
+        <v>0.383</v>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>0.171</v>
+        <v>0.195</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.139</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>0.128</v>
+        <v>0.366</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>0.104</v>
+        <v>0.287</v>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>0.34</v>
+        <v>0.231</v>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>0.31</v>
+        <v>0.258</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>0.144</v>
+        <v>0.318</v>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>0.298</v>
+        <v>0.104</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0.24</v>
+        <v>0.259</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>0.363</v>
+        <v>0.275</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>0.089</v>
+        <v>0.191</v>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>0.313</v>
+        <v>0.361</v>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>0.361</v>
+        <v>0.233</v>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>0.414</v>
+        <v>0.108</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>0.318</v>
+        <v>0.118</v>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>0.317</v>
+        <v>0.298</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>0.179</v>
+        <v>0.105</v>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>0.285</v>
+        <v>0.234</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>0.124</v>
+        <v>0.269</v>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>0.274</v>
+        <v>0.41</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>0.23</v>
+        <v>0.347</v>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>0.261</v>
+        <v>0.112</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>0.134</v>
+        <v>0.217</v>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>0.386</v>
+        <v>0.148</v>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>0.136</v>
+        <v>0.252</v>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>0.382</v>
+        <v>0.175</v>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>0.26</v>
+        <v>0.094</v>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>0.186</v>
+        <v>0.328</v>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>0.214</v>
+        <v>0.304</v>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>0.099</v>
+        <v>0.166</v>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>0.389</v>
+        <v>0.301</v>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>0.412</v>
+        <v>0.198</v>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>0.285</v>
+        <v>0.323</v>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>0.173</v>
+        <v>0.209</v>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>0.315</v>
+        <v>0.302</v>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>0.156</v>
+        <v>0.247</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>0.313</v>
+        <v>0.201</v>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>0.098</v>
+        <v>0.381</v>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>0.406</v>
+        <v>0.19</v>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>0.159</v>
+        <v>0.188</v>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>0.13</v>
+        <v>0.105</v>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>0.145</v>
+        <v>0.205</v>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>0.256</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>0.339</v>
+        <v>0.41</v>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>0.346</v>
+        <v>0.177</v>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>0.351</v>
+        <v>0.262</v>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>0.306</v>
+        <v>0.381</v>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>0.368</v>
+        <v>0.202</v>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>0.353</v>
+        <v>0.159</v>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>0.374</v>
+        <v>0.258</v>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>0.103</v>
+        <v>0.354</v>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>0.245</v>
+        <v>0.401</v>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>0.322</v>
+        <v>0.237</v>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="F171" s="2" t="n">
-        <v>0.114</v>
+        <v>0.343</v>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>0.268</v>
+        <v>0.235</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="F173" s="2" t="n">
-        <v>0.413</v>
+        <v>0.167</v>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>0.328</v>
+        <v>0.121</v>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="F175" s="2" t="n">
-        <v>0.23</v>
+        <v>0.131</v>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>0.259</v>
+        <v>0.155</v>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>0.24</v>
+        <v>0.227</v>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>0.144</v>
+        <v>0.147</v>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>0.319</v>
+        <v>0.162</v>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>0.181</v>
+        <v>0.356</v>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="F181" s="2" t="n">
-        <v>0.287</v>
+        <v>0.14</v>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>0.092</v>
+        <v>0.089</v>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         </is>
       </c>
       <c r="F183" s="2" t="n">
-        <v>0.27</v>
+        <v>0.313</v>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>0.297</v>
+        <v>0.185</v>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="F185" s="2" t="n">
-        <v>0.178</v>
+        <v>0.349</v>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="F186" s="2" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="F187" s="2" t="n">
-        <v>0.26</v>
+        <v>0.307</v>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>0.208</v>
+        <v>0.386</v>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="F189" s="2" t="n">
-        <v>0.413</v>
+        <v>0.239</v>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         </is>
       </c>
       <c r="F190" s="2" t="n">
-        <v>0.094</v>
+        <v>0.398</v>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="F191" s="2" t="n">
-        <v>0.183</v>
+        <v>0.242</v>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>0.414</v>
+        <v>0.222</v>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         </is>
       </c>
       <c r="F193" s="2" t="n">
-        <v>0.311</v>
+        <v>0.371</v>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>0.401</v>
+        <v>0.355</v>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="F195" s="2" t="n">
-        <v>0.249</v>
+        <v>0.369</v>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>0.145</v>
+        <v>0.272</v>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="F197" s="2" t="n">
-        <v>0.286</v>
+        <v>0.099</v>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>0.306</v>
+        <v>0.137</v>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="F199" s="2" t="n">
-        <v>0.216</v>
+        <v>0.322</v>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         </is>
       </c>
       <c r="F200" s="2" t="n">
-        <v>0.133</v>
+        <v>0.298</v>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="F201" s="2" t="n">
-        <v>0.139</v>
+        <v>0.114</v>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="F202" s="2" t="n">
-        <v>0.083</v>
+        <v>0.237</v>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         </is>
       </c>
       <c r="F203" s="2" t="n">
-        <v>0.408</v>
+        <v>0.083</v>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="F204" s="2" t="n">
-        <v>0.252</v>
+        <v>0.175</v>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="F205" s="2" t="n">
-        <v>0.264</v>
+        <v>0.127</v>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="F206" s="2" t="n">
-        <v>0.108</v>
+        <v>0.411</v>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="F207" s="2" t="n">
-        <v>0.263</v>
+        <v>0.14</v>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>0.274</v>
+        <v>0.401</v>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="F209" s="2" t="n">
-        <v>0.172</v>
+        <v>0.153</v>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>0.169</v>
+        <v>0.081</v>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="F211" s="2" t="n">
-        <v>0.166</v>
+        <v>0.419</v>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="F212" s="2" t="n">
-        <v>0.108</v>
+        <v>0.116</v>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="F213" s="2" t="n">
-        <v>0.381</v>
+        <v>0.363</v>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>0.382</v>
+        <v>0.41</v>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="F215" s="2" t="n">
-        <v>0.194</v>
+        <v>0.125</v>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="F216" s="2" t="n">
-        <v>0.136</v>
+        <v>0.148</v>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="F217" s="2" t="n">
-        <v>0.092</v>
+        <v>0.365</v>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="F218" s="2" t="n">
-        <v>0.355</v>
+        <v>0.153</v>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="F219" s="2" t="n">
-        <v>0.136</v>
+        <v>0.225</v>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="F220" s="2" t="n">
-        <v>0.295</v>
+        <v>0.116</v>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="F221" s="2" t="n">
-        <v>0.148</v>
+        <v>0.267</v>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="F222" s="2" t="n">
-        <v>0.232</v>
+        <v>0.08</v>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="F223" s="2" t="n">
-        <v>0.126</v>
+        <v>0.371</v>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         </is>
       </c>
       <c r="F224" s="2" t="n">
-        <v>0.139</v>
+        <v>0.165</v>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="F225" s="2" t="n">
-        <v>0.354</v>
+        <v>0.274</v>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         </is>
       </c>
       <c r="F226" s="2" t="n">
-        <v>0.089</v>
+        <v>0.126</v>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         </is>
       </c>
       <c r="F227" s="2" t="n">
-        <v>0.188</v>
+        <v>0.418</v>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="F228" s="2" t="n">
-        <v>0.318</v>
+        <v>0.24</v>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         </is>
       </c>
       <c r="F229" s="2" t="n">
-        <v>0.135</v>
+        <v>0.217</v>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>0.177</v>
+        <v>0.206</v>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="F231" s="2" t="n">
-        <v>0.364</v>
+        <v>0.31</v>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         </is>
       </c>
       <c r="F232" s="2" t="n">
-        <v>0.276</v>
+        <v>0.242</v>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="F233" s="2" t="n">
-        <v>0.132</v>
+        <v>0.167</v>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="F234" s="2" t="n">
-        <v>0.332</v>
+        <v>0.116</v>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         </is>
       </c>
       <c r="F235" s="2" t="n">
-        <v>0.33</v>
+        <v>0.296</v>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="F236" s="2" t="n">
-        <v>0.107</v>
+        <v>0.418</v>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="F237" s="2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="F238" s="2" t="n">
-        <v>0.138</v>
+        <v>0.36</v>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         </is>
       </c>
       <c r="F239" s="2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="F240" s="2" t="n">
-        <v>0.349</v>
+        <v>0.211</v>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>0.287</v>
+        <v>0.222</v>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>0.267</v>
+        <v>0.115</v>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>0.221</v>
+        <v>0.329</v>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="F244" s="2" t="n">
-        <v>0.407</v>
+        <v>0.415</v>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         </is>
       </c>
       <c r="F245" s="2" t="n">
-        <v>0.33</v>
+        <v>0.191</v>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>0.212</v>
+        <v>0.171</v>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         </is>
       </c>
       <c r="F247" s="2" t="n">
-        <v>0.198</v>
+        <v>0.149</v>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>0.346</v>
+        <v>0.332</v>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         </is>
       </c>
       <c r="F249" s="2" t="n">
-        <v>0.09</v>
+        <v>0.285</v>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>0.392</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         </is>
       </c>
       <c r="F251" s="2" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         </is>
       </c>
       <c r="F252" s="2" t="n">
-        <v>0.242</v>
+        <v>0.116</v>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         </is>
       </c>
       <c r="F253" s="2" t="n">
-        <v>0.195</v>
+        <v>0.104</v>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>0.158</v>
+        <v>0.335</v>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="F255" s="2" t="n">
-        <v>0.129</v>
+        <v>0.415</v>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         </is>
       </c>
       <c r="F256" s="2" t="n">
-        <v>0.35</v>
+        <v>0.414</v>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="F257" s="2" t="n">
-        <v>0.24</v>
+        <v>0.378</v>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>0.239</v>
+        <v>0.329</v>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="F259" s="2" t="n">
-        <v>0.281</v>
+        <v>0.167</v>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>0.116</v>
+        <v>0.214</v>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         </is>
       </c>
       <c r="F261" s="2" t="n">
-        <v>0.236</v>
+        <v>0.271</v>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>0.217</v>
+        <v>0.143</v>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="F263" s="2" t="n">
-        <v>0.285</v>
+        <v>0.165</v>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>0.131</v>
+        <v>0.351</v>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="F265" s="2" t="n">
-        <v>0.39</v>
+        <v>0.091</v>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         </is>
       </c>
       <c r="F266" s="2" t="n">
-        <v>0.169</v>
+        <v>0.135</v>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>0.163</v>
+        <v>0.273</v>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         </is>
       </c>
       <c r="F269" s="2" t="n">
-        <v>0.109</v>
+        <v>0.4</v>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="F270" s="2" t="n">
-        <v>0.154</v>
+        <v>0.081</v>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         </is>
       </c>
       <c r="F271" s="2" t="n">
-        <v>0.378</v>
+        <v>0.328</v>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         </is>
       </c>
       <c r="F272" s="2" t="n">
-        <v>0.382</v>
+        <v>0.271</v>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         </is>
       </c>
       <c r="F273" s="2" t="n">
-        <v>0.233</v>
+        <v>0.297</v>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>0.273</v>
+        <v>0.308</v>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         </is>
       </c>
       <c r="F275" s="2" t="n">
-        <v>0.299</v>
+        <v>0.353</v>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>0.371</v>
+        <v>0.164</v>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         </is>
       </c>
       <c r="F277" s="2" t="n">
-        <v>0.196</v>
+        <v>0.244</v>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         </is>
       </c>
       <c r="F278" s="2" t="n">
-        <v>0.082</v>
+        <v>0.107</v>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="F279" s="2" t="n">
-        <v>0.31</v>
+        <v>0.267</v>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>0.167</v>
+        <v>0.235</v>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="F281" s="2" t="n">
-        <v>0.375</v>
+        <v>0.291</v>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>0.104</v>
+        <v>0.204</v>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="F283" s="2" t="n">
-        <v>0.243</v>
+        <v>0.276</v>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>0.363</v>
+        <v>0.309</v>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>0.323</v>
+        <v>0.367</v>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>0.177</v>
+        <v>0.397</v>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>0.163</v>
+        <v>0.146</v>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>0.202</v>
+        <v>0.082</v>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>0.159</v>
+        <v>0.147</v>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>0.117</v>
+        <v>0.292</v>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>0.211</v>
+        <v>0.146</v>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>0.186</v>
+        <v>0.372</v>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="F293" s="2" t="n">
-        <v>0.41</v>
+        <v>0.092</v>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>0.262</v>
+        <v>0.344</v>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>0.358</v>
+        <v>0.221</v>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>0.246</v>
+        <v>0.145</v>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>0.183</v>
+        <v>0.303</v>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>0.148</v>
+        <v>0.097</v>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>0.297</v>
+        <v>0.324</v>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.257</v>
+        <v>0.118</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.301</v>
+        <v>0.151</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.342</v>
+        <v>0.138</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.149</v>
+        <v>0.349</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.199</v>
+        <v>0.313</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.265</v>
+        <v>0.278</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.339</v>
+        <v>0.104</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.337</v>
+        <v>0.192</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.201</v>
+        <v>0.264</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.194</v>
+        <v>0.239</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.383</v>
+        <v>0.195</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.28</v>
+        <v>0.213</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.229</v>
+        <v>0.368</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.128</v>
+        <v>0.309</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.395</v>
+        <v>0.149</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.111</v>
+        <v>0.162</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.099</v>
+        <v>0.164</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.179</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.177</v>
+        <v>0.396</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.09</v>
+        <v>0.408</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.326</v>
+        <v>0.264</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.376</v>
+        <v>0.245</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.203</v>
+        <v>0.154</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.091</v>
+        <v>0.378</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.326</v>
+        <v>0.386</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.373</v>
+        <v>0.261</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.336</v>
+        <v>0.358</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.279</v>
+        <v>0.14</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.408</v>
+        <v>0.219</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.131</v>
+        <v>0.201</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.157</v>
+        <v>0.116</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.169</v>
+        <v>0.172</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.123</v>
+        <v>0.3</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.345</v>
+        <v>0.41</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.389</v>
+        <v>0.17</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.126</v>
+        <v>0.089</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.221</v>
+        <v>0.303</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.331</v>
+        <v>0.322</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.337</v>
+        <v>0.206</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.125</v>
+        <v>0.234</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.36</v>
+        <v>0.106</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.287</v>
+        <v>0.411</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.14</v>
+        <v>0.238</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.259</v>
+        <v>0.189</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.09</v>
+        <v>0.325</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.244</v>
+        <v>0.124</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.194</v>
+        <v>0.124</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.35</v>
+        <v>0.188</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.345</v>
+        <v>0.147</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.39</v>
+        <v>0.307</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.282</v>
+        <v>0.297</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.396</v>
+        <v>0.223</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.189</v>
+        <v>0.313</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.224</v>
+        <v>0.229</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.101</v>
+        <v>0.42</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.131</v>
+        <v>0.183</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.207</v>
+        <v>0.174</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.155</v>
+        <v>0.336</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.398</v>
+        <v>0.262</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.419</v>
+        <v>0.284</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.097</v>
+        <v>0.4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.217</v>
+        <v>0.155</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.135</v>
+        <v>0.154</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.092</v>
+        <v>0.406</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.376</v>
+        <v>0.188</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.175</v>
+        <v>0.327</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.162</v>
+        <v>0.096</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.27</v>
+        <v>0.345</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.351</v>
+        <v>0.115</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.197</v>
+        <v>0.297</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.412</v>
+        <v>0.347</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.326</v>
+        <v>0.206</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.206</v>
+        <v>0.324</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.375</v>
+        <v>0.242</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.366</v>
+        <v>0.29</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.2</v>
+        <v>0.158</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.107</v>
+        <v>0.335</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0.272</v>
+        <v>0.245</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0.277</v>
+        <v>0.186</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0.395</v>
+        <v>0.188</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.35</v>
+        <v>0.112</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.15</v>
+        <v>0.224</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.285</v>
+        <v>0.132</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0.248</v>
+        <v>0.288</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.226</v>
+        <v>0.244</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0.151</v>
+        <v>0.273</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0.113</v>
+        <v>0.395</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.411</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0.265</v>
+        <v>0.396</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0.179</v>
+        <v>0.304</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0.328</v>
+        <v>0.216</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0.303</v>
+        <v>0.345</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.121</v>
+        <v>0.081</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0.218</v>
+        <v>0.419</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.172</v>
+        <v>0.294</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0.129</v>
+        <v>0.214</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.241</v>
+        <v>0.277</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0.283</v>
+        <v>0.29</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.238</v>
+        <v>0.369</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.26</v>
+        <v>0.109</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0.244</v>
+        <v>0.235</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0.31</v>
+        <v>0.109</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0.294</v>
+        <v>0.108</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0.195</v>
+        <v>0.415</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.368</v>
+        <v>0.28</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.329</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.334</v>
+        <v>0.288</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.39</v>
+        <v>0.133</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0.326</v>
+        <v>0.347</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0.263</v>
+        <v>0.368</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0.34</v>
+        <v>0.232</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0.23</v>
+        <v>0.254</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0.207</v>
+        <v>0.296</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0.144</v>
+        <v>0.136</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0.175</v>
+        <v>0.383</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0.171</v>
+        <v>0.195</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0.139</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0.128</v>
+        <v>0.366</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0.104</v>
+        <v>0.287</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0.34</v>
+        <v>0.231</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0.31</v>
+        <v>0.258</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0.144</v>
+        <v>0.318</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0.298</v>
+        <v>0.104</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0.24</v>
+        <v>0.259</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0.363</v>
+        <v>0.275</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>0.089</v>
+        <v>0.191</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>0.313</v>
+        <v>0.361</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0.361</v>
+        <v>0.233</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0.414</v>
+        <v>0.108</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>0.318</v>
+        <v>0.118</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0.317</v>
+        <v>0.298</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0.179</v>
+        <v>0.105</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.285</v>
+        <v>0.234</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0.124</v>
+        <v>0.269</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0.274</v>
+        <v>0.41</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0.23</v>
+        <v>0.347</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0.261</v>
+        <v>0.112</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0.134</v>
+        <v>0.217</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0.386</v>
+        <v>0.148</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0.136</v>
+        <v>0.252</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0.382</v>
+        <v>0.175</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0.26</v>
+        <v>0.094</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0.186</v>
+        <v>0.328</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0.214</v>
+        <v>0.304</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0.099</v>
+        <v>0.166</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>0.389</v>
+        <v>0.301</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0.412</v>
+        <v>0.198</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0.285</v>
+        <v>0.323</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0.173</v>
+        <v>0.209</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0.315</v>
+        <v>0.302</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>0.156</v>
+        <v>0.247</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.416</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>0.313</v>
+        <v>0.201</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>0.098</v>
+        <v>0.381</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0.406</v>
+        <v>0.19</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0.159</v>
+        <v>0.188</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0.13</v>
+        <v>0.105</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0.145</v>
+        <v>0.205</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>0.256</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>0.339</v>
+        <v>0.41</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>0.346</v>
+        <v>0.177</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0.351</v>
+        <v>0.262</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0.306</v>
+        <v>0.381</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0.368</v>
+        <v>0.202</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0.353</v>
+        <v>0.159</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>0.374</v>
+        <v>0.258</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>0.103</v>
+        <v>0.354</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>0.245</v>
+        <v>0.401</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>0.322</v>
+        <v>0.237</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>0.114</v>
+        <v>0.343</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>0.268</v>
+        <v>0.235</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>0.413</v>
+        <v>0.167</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0.328</v>
+        <v>0.121</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>0.23</v>
+        <v>0.131</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>0.259</v>
+        <v>0.155</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>0.24</v>
+        <v>0.227</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>0.144</v>
+        <v>0.147</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>0.319</v>
+        <v>0.162</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>0.181</v>
+        <v>0.356</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>0.287</v>
+        <v>0.14</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>0.092</v>
+        <v>0.089</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>0.27</v>
+        <v>0.313</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>0.297</v>
+        <v>0.185</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>0.178</v>
+        <v>0.349</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>0.26</v>
+        <v>0.307</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>0.208</v>
+        <v>0.386</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>0.413</v>
+        <v>0.239</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>0.094</v>
+        <v>0.398</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>0.183</v>
+        <v>0.242</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>0.414</v>
+        <v>0.222</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>0.311</v>
+        <v>0.371</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>0.401</v>
+        <v>0.355</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0.249</v>
+        <v>0.369</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>0.145</v>
+        <v>0.272</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>0.286</v>
+        <v>0.099</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>0.306</v>
+        <v>0.137</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>0.216</v>
+        <v>0.322</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>0.133</v>
+        <v>0.298</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>0.139</v>
+        <v>0.114</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>0.083</v>
+        <v>0.237</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>0.408</v>
+        <v>0.083</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>0.252</v>
+        <v>0.175</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>0.264</v>
+        <v>0.127</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>0.108</v>
+        <v>0.411</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>0.263</v>
+        <v>0.14</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>0.274</v>
+        <v>0.401</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>0.172</v>
+        <v>0.153</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>0.169</v>
+        <v>0.081</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>0.166</v>
+        <v>0.419</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>0.108</v>
+        <v>0.116</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>0.381</v>
+        <v>0.363</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>0.382</v>
+        <v>0.41</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>0.194</v>
+        <v>0.125</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>0.136</v>
+        <v>0.148</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>0.092</v>
+        <v>0.365</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>0.355</v>
+        <v>0.153</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>0.136</v>
+        <v>0.225</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>0.295</v>
+        <v>0.116</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>0.148</v>
+        <v>0.267</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>0.232</v>
+        <v>0.08</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>0.126</v>
+        <v>0.371</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>0.139</v>
+        <v>0.165</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>0.354</v>
+        <v>0.274</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>0.089</v>
+        <v>0.126</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>0.188</v>
+        <v>0.418</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>0.318</v>
+        <v>0.24</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>0.135</v>
+        <v>0.217</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>0.177</v>
+        <v>0.206</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>0.364</v>
+        <v>0.31</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>0.276</v>
+        <v>0.242</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>0.132</v>
+        <v>0.167</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>0.332</v>
+        <v>0.116</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>0.33</v>
+        <v>0.296</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>0.107</v>
+        <v>0.418</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>0.138</v>
+        <v>0.36</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.178</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>0.349</v>
+        <v>0.211</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>0.287</v>
+        <v>0.222</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>0.267</v>
+        <v>0.115</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>0.221</v>
+        <v>0.329</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>0.407</v>
+        <v>0.415</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>0.33</v>
+        <v>0.191</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>0.212</v>
+        <v>0.171</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>0.198</v>
+        <v>0.149</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>0.346</v>
+        <v>0.332</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>0.09</v>
+        <v>0.285</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>0.392</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>0.112</v>
+        <v>0.116</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>0.242</v>
+        <v>0.116</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>0.195</v>
+        <v>0.104</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>0.158</v>
+        <v>0.335</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>0.129</v>
+        <v>0.415</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>0.35</v>
+        <v>0.414</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>0.24</v>
+        <v>0.378</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>0.239</v>
+        <v>0.329</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>0.281</v>
+        <v>0.167</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>0.116</v>
+        <v>0.214</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>0.236</v>
+        <v>0.271</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>0.217</v>
+        <v>0.143</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>0.285</v>
+        <v>0.165</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>0.131</v>
+        <v>0.351</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>0.39</v>
+        <v>0.091</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>0.169</v>
+        <v>0.135</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>0.163</v>
+        <v>0.273</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>0.109</v>
+        <v>0.4</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>0.154</v>
+        <v>0.081</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>0.378</v>
+        <v>0.328</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>0.382</v>
+        <v>0.271</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>0.233</v>
+        <v>0.297</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>0.273</v>
+        <v>0.308</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>0.299</v>
+        <v>0.353</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>0.371</v>
+        <v>0.164</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>0.196</v>
+        <v>0.244</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>0.082</v>
+        <v>0.107</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>0.31</v>
+        <v>0.267</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>0.167</v>
+        <v>0.235</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>0.375</v>
+        <v>0.291</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>0.104</v>
+        <v>0.204</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>0.243</v>
+        <v>0.276</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>0.363</v>
+        <v>0.309</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>0.323</v>
+        <v>0.367</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>0.177</v>
+        <v>0.397</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>0.163</v>
+        <v>0.146</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>0.202</v>
+        <v>0.082</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>0.159</v>
+        <v>0.147</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>0.117</v>
+        <v>0.292</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>0.211</v>
+        <v>0.146</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>0.186</v>
+        <v>0.372</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>0.41</v>
+        <v>0.092</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>0.262</v>
+        <v>0.344</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>0.358</v>
+        <v>0.221</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>0.246</v>
+        <v>0.145</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         </is>
       </c>
       <c r="F297" t="n">
-        <v>0.257</v>
+        <v>0.256</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>0.183</v>
+        <v>0.303</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>0.148</v>
+        <v>0.097</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>0.297</v>
+        <v>0.324</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72.36</v>
+        <v>72.92</v>
       </c>
     </row>
     <row r="10">
@@ -30851,7 +30851,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-12 09:55:14</t>
+          <t>2026-08-12 11:08:42</t>
         </is>
       </c>
     </row>

--- a/automation/reports/Excel/Vulnerability_Test_Report.xlsx
+++ b/automation/reports/Excel/Vulnerability_Test_Report.xlsx
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.118</v>
+        <v>0.379</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.151</v>
+        <v>0.156</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.138</v>
+        <v>0.375</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.349</v>
+        <v>0.223</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.313</v>
+        <v>0.367</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.278</v>
+        <v>0.259</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.104</v>
+        <v>0.17</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.192</v>
+        <v>0.222</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.264</v>
+        <v>0.322</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.239</v>
+        <v>0.377</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.195</v>
+        <v>0.345</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.213</v>
+        <v>0.303</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.368</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.309</v>
+        <v>0.415</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.149</v>
+        <v>0.28</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.162</v>
+        <v>0.383</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.164</v>
+        <v>0.094</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.319</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.396</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.408</v>
+        <v>0.407</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0.264</v>
+        <v>0.405</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0.245</v>
+        <v>0.096</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0.154</v>
+        <v>0.29</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0.378</v>
+        <v>0.143</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0.386</v>
+        <v>0.121</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.261</v>
+        <v>0.154</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>0.358</v>
+        <v>0.264</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.14</v>
+        <v>0.412</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.219</v>
+        <v>0.345</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>0.201</v>
+        <v>0.203</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.116</v>
+        <v>0.384</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>0.172</v>
+        <v>0.38</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>0.3</v>
+        <v>0.297</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>0.41</v>
+        <v>0.412</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>0.17</v>
+        <v>0.126</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>0.089</v>
+        <v>0.409</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>0.303</v>
+        <v>0.116</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>0.322</v>
+        <v>0.334</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.206</v>
+        <v>0.305</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>0.234</v>
+        <v>0.302</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>0.106</v>
+        <v>0.264</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>0.411</v>
+        <v>0.32</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>0.238</v>
+        <v>0.366</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>0.189</v>
+        <v>0.137</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>0.325</v>
+        <v>0.373</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>0.124</v>
+        <v>0.188</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>0.124</v>
+        <v>0.236</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>0.188</v>
+        <v>0.241</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>0.147</v>
+        <v>0.131</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.307</v>
+        <v>0.262</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>0.297</v>
+        <v>0.315</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>0.223</v>
+        <v>0.282</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>0.313</v>
+        <v>0.233</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>0.229</v>
+        <v>0.277</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>0.42</v>
+        <v>0.325</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>0.183</v>
+        <v>0.287</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>0.174</v>
+        <v>0.189</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>0.336</v>
+        <v>0.267</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>0.262</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>0.284</v>
+        <v>0.344</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>0.4</v>
+        <v>0.388</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>0.155</v>
+        <v>0.357</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>0.154</v>
+        <v>0.219</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>0.406</v>
+        <v>0.125</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>0.188</v>
+        <v>0.351</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>0.327</v>
+        <v>0.118</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.096</v>
+        <v>0.384</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>0.345</v>
+        <v>0.377</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>0.115</v>
+        <v>0.138</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>0.297</v>
+        <v>0.243</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>0.347</v>
+        <v>0.268</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>0.206</v>
+        <v>0.41</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>0.324</v>
+        <v>0.406</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>0.242</v>
+        <v>0.365</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>0.29</v>
+        <v>0.323</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>0.158</v>
+        <v>0.292</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>0.335</v>
+        <v>0.113</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>0.245</v>
+        <v>0.235</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>0.186</v>
+        <v>0.11</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>0.188</v>
+        <v>0.167</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>0.112</v>
+        <v>0.387</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.224</v>
+        <v>0.313</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>0.132</v>
+        <v>0.18</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0.288</v>
+        <v>0.337</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>0.244</v>
+        <v>0.142</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>0.273</v>
+        <v>0.229</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0.395</v>
+        <v>0.394</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0.411</v>
+        <v>0.248</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>0.396</v>
+        <v>0.145</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>0.304</v>
+        <v>0.376</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>0.216</v>
+        <v>0.276</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>0.345</v>
+        <v>0.33</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>0.081</v>
+        <v>0.311</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>0.419</v>
+        <v>0.137</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>0.294</v>
+        <v>0.168</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>0.214</v>
+        <v>0.254</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>0.277</v>
+        <v>0.396</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>0.29</v>
+        <v>0.359</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.369</v>
+        <v>0.244</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0.109</v>
+        <v>0.153</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0.235</v>
+        <v>0.232</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>0.109</v>
+        <v>0.192</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>0.108</v>
+        <v>0.273</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>0.415</v>
+        <v>0.224</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>0.329</v>
+        <v>0.36</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="F108" s="2" t="n">
-        <v>0.288</v>
+        <v>0.188</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>0.133</v>
+        <v>0.214</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>0.347</v>
+        <v>0.08</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="F111" s="2" t="n">
-        <v>0.368</v>
+        <v>0.303</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>0.232</v>
+        <v>0.391</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>0.254</v>
+        <v>0.122</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>0.296</v>
+        <v>0.319</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>0.383</v>
+        <v>0.381</v>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>0.195</v>
+        <v>0.134</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>0.366</v>
+        <v>0.096</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>0.287</v>
+        <v>0.222</v>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="F121" s="2" t="n">
-        <v>0.231</v>
+        <v>0.33</v>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         </is>
       </c>
       <c r="F122" s="2" t="n">
-        <v>0.258</v>
+        <v>0.125</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>0.318</v>
+        <v>0.126</v>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>0.104</v>
+        <v>0.391</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>0.259</v>
+        <v>0.14</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         </is>
       </c>
       <c r="F126" s="2" t="n">
-        <v>0.275</v>
+        <v>0.374</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="F127" s="2" t="n">
-        <v>0.191</v>
+        <v>0.143</v>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="F128" s="2" t="n">
-        <v>0.361</v>
+        <v>0.096</v>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="F129" s="2" t="n">
-        <v>0.233</v>
+        <v>0.277</v>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="F130" s="2" t="n">
-        <v>0.108</v>
+        <v>0.329</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>0.118</v>
+        <v>0.095</v>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>0.298</v>
+        <v>0.219</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>0.105</v>
+        <v>0.394</v>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>0.234</v>
+        <v>0.398</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>0.269</v>
+        <v>0.095</v>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>0.41</v>
+        <v>0.083</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="F137" s="2" t="n">
-        <v>0.347</v>
+        <v>0.242</v>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>0.112</v>
+        <v>0.265</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>0.217</v>
+        <v>0.254</v>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>0.148</v>
+        <v>0.239</v>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>0.252</v>
+        <v>0.204</v>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>0.175</v>
+        <v>0.255</v>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>0.094</v>
+        <v>0.137</v>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>0.328</v>
+        <v>0.181</v>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>0.304</v>
+        <v>0.38</v>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
         </is>
       </c>
       <c r="F146" s="2" t="n">
-        <v>0.166</v>
+        <v>0.313</v>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="F147" s="2" t="n">
-        <v>0.301</v>
+        <v>0.143</v>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="F148" s="2" t="n">
-        <v>0.198</v>
+        <v>0.095</v>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="F149" s="2" t="n">
-        <v>0.323</v>
+        <v>0.325</v>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>0.209</v>
+        <v>0.39</v>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>0.302</v>
+        <v>0.125</v>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="F152" s="2" t="n">
-        <v>0.247</v>
+        <v>0.33</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>0.416</v>
+        <v>0.401</v>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="F154" s="2" t="n">
-        <v>0.201</v>
+        <v>0.27</v>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="F155" s="2" t="n">
-        <v>0.381</v>
+        <v>0.292</v>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="F156" s="2" t="n">
-        <v>0.19</v>
+        <v>0.258</v>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="F157" s="2" t="n">
-        <v>0.188</v>
+        <v>0.237</v>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="F158" s="2" t="n">
-        <v>0.105</v>
+        <v>0.366</v>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="F159" s="2" t="n">
-        <v>0.205</v>
+        <v>0.36</v>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="F160" s="2" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         </is>
       </c>
       <c r="F161" s="2" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>0.177</v>
+        <v>0.291</v>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>0.262</v>
+        <v>0.172</v>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>0.381</v>
+        <v>0.082</v>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>0.202</v>
+        <v>0.173</v>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>0.159</v>
+        <v>0.257</v>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>0.258</v>
+        <v>0.153</v>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         </is>
       </c>
       <c r="F168" s="2" t="n">
-        <v>0.354</v>
+        <v>0.375</v>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="F169" s="2" t="n">
-        <v>0.401</v>
+        <v>0.313</v>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         </is>
       </c>
       <c r="F170" s="2" t="n">
-        <v>0.237</v>
+        <v>0.159</v>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="F171" s="2" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         </is>
       </c>
       <c r="F172" s="2" t="n">
-        <v>0.235</v>
+        <v>0.332</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="F173" s="2" t="n">
-        <v>0.167</v>
+        <v>0.095</v>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="F174" s="2" t="n">
-        <v>0.121</v>
+        <v>0.135</v>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         </is>
       </c>
       <c r="F175" s="2" t="n">
-        <v>0.131</v>
+        <v>0.213</v>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="F176" s="2" t="n">
-        <v>0.155</v>
+        <v>0.304</v>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="F177" s="2" t="n">
-        <v>0.227</v>
+        <v>0.251</v>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="F178" s="2" t="n">
-        <v>0.147</v>
+        <v>0.258</v>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="F179" s="2" t="n">
-        <v>0.162</v>
+        <v>0.211</v>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="F180" s="2" t="n">
-        <v>0.356</v>
+        <v>0.157</v>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="F181" s="2" t="n">
-        <v>0.14</v>
+        <v>0.397</v>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="F182" s="2" t="n">
-        <v>0.089</v>
+        <v>0.341</v>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         </is>
       </c>
       <c r="F183" s="2" t="n">
-        <v>0.313</v>
+        <v>0.4</v>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         </is>
       </c>
       <c r="F184" s="2" t="n">
-        <v>0.185</v>
+        <v>0.223</v>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="F185" s="2" t="n">
-        <v>0.349</v>
+        <v>0.31</v>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="F186" s="2" t="n">
-        <v>0.3</v>
+        <v>0.226</v>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         </is>
       </c>
       <c r="F187" s="2" t="n">
-        <v>0.307</v>
+        <v>0.359</v>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="F188" s="2" t="n">
-        <v>0.386</v>
+        <v>0.309</v>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="F189" s="2" t="n">
-        <v>0.239</v>
+        <v>0.201</v>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         </is>
       </c>
       <c r="F190" s="2" t="n">
-        <v>0.398</v>
+        <v>0.252</v>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="F191" s="2" t="n">
-        <v>0.242</v>
+        <v>0.095</v>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="F192" s="2" t="n">
-        <v>0.222</v>
+        <v>0.184</v>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         </is>
       </c>
       <c r="F193" s="2" t="n">
-        <v>0.371</v>
+        <v>0.305</v>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         </is>
       </c>
       <c r="F194" s="2" t="n">
-        <v>0.355</v>
+        <v>0.346</v>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         </is>
       </c>
       <c r="F195" s="2" t="n">
-        <v>0.369</v>
+        <v>0.154</v>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         </is>
       </c>
       <c r="F196" s="2" t="n">
-        <v>0.272</v>
+        <v>0.302</v>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="F197" s="2" t="n">
-        <v>0.099</v>
+        <v>0.399</v>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>0.137</v>
+        <v>0.322</v>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         </is>
       </c>
       <c r="F199" s="2" t="n">
-        <v>0.322</v>
+        <v>0.24</v>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         </is>
       </c>
       <c r="F200" s="2" t="n">
-        <v>0.298</v>
+        <v>0.115</v>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="F201" s="2" t="n">
-        <v>0.114</v>
+        <v>0.385</v>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         </is>
       </c>
       <c r="F202" s="2" t="n">
-        <v>0.237</v>
+        <v>0.098</v>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         </is>
       </c>
       <c r="F203" s="2" t="n">
-        <v>0.083</v>
+        <v>0.231</v>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         </is>
       </c>
       <c r="F204" s="2" t="n">
-        <v>0.175</v>
+        <v>0.115</v>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="F205" s="2" t="n">
-        <v>0.127</v>
+        <v>0.301</v>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="F206" s="2" t="n">
-        <v>0.411</v>
+        <v>0.192</v>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         </is>
       </c>
       <c r="F207" s="2" t="n">
-        <v>0.14</v>
+        <v>0.163</v>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>0.401</v>
+        <v>0.189</v>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         </is>
       </c>
       <c r="F209" s="2" t="n">
-        <v>0.153</v>
+        <v>0.221</v>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         </is>
       </c>
       <c r="F210" s="2" t="n">
-        <v>0.081</v>
+        <v>0.17</v>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="F211" s="2" t="n">
-        <v>0.419</v>
+        <v>0.213</v>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="F212" s="2" t="n">
-        <v>0.116</v>
+        <v>0.159</v>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         </is>
       </c>
       <c r="F213" s="2" t="n">
-        <v>0.363</v>
+        <v>0.299</v>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         </is>
       </c>
       <c r="F214" s="2" t="n">
-        <v>0.41</v>
+        <v>0.13</v>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="F215" s="2" t="n">
-        <v>0.125</v>
+        <v>0.319</v>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="F216" s="2" t="n">
-        <v>0.148</v>
+        <v>0.317</v>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="F217" s="2" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         </is>
       </c>
       <c r="F218" s="2" t="n">
-        <v>0.153</v>
+        <v>0.209</v>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="F219" s="2" t="n">
-        <v>0.225</v>
+        <v>0.407</v>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         </is>
       </c>
       <c r="F220" s="2" t="n">
-        <v>0.116</v>
+        <v>0.113</v>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="F221" s="2" t="n">
-        <v>0.267</v>
+        <v>0.361</v>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="F222" s="2" t="n">
-        <v>0.08</v>
+        <v>0.402</v>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="F223" s="2" t="n">
-        <v>0.371</v>
+        <v>0.15</v>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         </is>
       </c>
       <c r="F224" s="2" t="n">
-        <v>0.165</v>
+        <v>0.26</v>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         </is>
       </c>
       <c r="F225" s="2" t="n">
-        <v>0.274</v>
+        <v>0.25</v>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         </is>
       </c>
       <c r="F226" s="2" t="n">
-        <v>0.126</v>
+        <v>0.19</v>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         </is>
       </c>
       <c r="F227" s="2" t="n">
-        <v>0.418</v>
+        <v>0.153</v>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="F228" s="2" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         </is>
       </c>
       <c r="F229" s="2" t="n">
-        <v>0.217</v>
+        <v>0.378</v>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="F231" s="2" t="n">
-        <v>0.31</v>
+        <v>0.233</v>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         </is>
       </c>
       <c r="F232" s="2" t="n">
-        <v>0.242</v>
+        <v>0.28</v>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         </is>
       </c>
       <c r="F233" s="2" t="n">
-        <v>0.167</v>
+        <v>0.255</v>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="F234" s="2" t="n">
-        <v>0.116</v>
+        <v>0.305</v>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         </is>
       </c>
       <c r="F235" s="2" t="n">
-        <v>0.296</v>
+        <v>0.335</v>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="F236" s="2" t="n">
-        <v>0.418</v>
+        <v>0.337</v>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         </is>
       </c>
       <c r="F237" s="2" t="n">
-        <v>0.14</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="F238" s="2" t="n">
-        <v>0.36</v>
+        <v>0.232</v>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         </is>
       </c>
       <c r="F239" s="2" t="n">
-        <v>0.178</v>
+        <v>0.383</v>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         </is>
       </c>
       <c r="F240" s="2" t="n">
-        <v>0.211</v>
+        <v>0.357</v>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>0.222</v>
+        <v>0.251</v>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>0.115</v>
+        <v>0.093</v>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>0.329</v>
+        <v>0.107</v>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         </is>
       </c>
       <c r="F244" s="2" t="n">
-        <v>0.415</v>
+        <v>0.377</v>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         </is>
       </c>
       <c r="F245" s="2" t="n">
-        <v>0.191</v>
+        <v>0.146</v>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>0.171</v>
+        <v>0.335</v>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         </is>
       </c>
       <c r="F247" s="2" t="n">
-        <v>0.149</v>
+        <v>0.249</v>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="F248" s="2" t="n">
-        <v>0.332</v>
+        <v>0.292</v>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         </is>
       </c>
       <c r="F249" s="2" t="n">
-        <v>0.285</v>
+        <v>0.352</v>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="F250" s="2" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         </is>
       </c>
       <c r="F251" s="2" t="n">
-        <v>0.116</v>
+        <v>0.262</v>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         </is>
       </c>
       <c r="F252" s="2" t="n">
-        <v>0.116</v>
+        <v>0.225</v>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         </is>
       </c>
       <c r="F253" s="2" t="n">
-        <v>0.104</v>
+        <v>0.366</v>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         </is>
       </c>
       <c r="F254" s="2" t="n">
-        <v>0.335</v>
+        <v>0.395</v>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="F255" s="2" t="n">
-        <v>0.415</v>
+        <v>0.117</v>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         </is>
       </c>
       <c r="F256" s="2" t="n">
-        <v>0.414</v>
+        <v>0.12</v>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         </is>
       </c>
       <c r="F257" s="2" t="n">
-        <v>0.378</v>
+        <v>0.136</v>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>0.329</v>
+        <v>0.26</v>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
@@ -13410,7 +13410,7 @@
         </is>
       </c>
       <c r="F259" s="2" t="n">
-        <v>0.167</v>
+        <v>0.165</v>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>0.214</v>
+        <v>0.309</v>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         </is>
       </c>
       <c r="F261" s="2" t="n">
-        <v>0.271</v>
+        <v>0.293</v>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>0.143</v>
+        <v>0.309</v>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         </is>
       </c>
       <c r="F263" s="2" t="n">
-        <v>0.165</v>
+        <v>0.323</v>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="F264" s="2" t="n">
-        <v>0.351</v>
+        <v>0.216</v>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         </is>
       </c>
       <c r="F265" s="2" t="n">
-        <v>0.091</v>
+        <v>0.218</v>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>0.273</v>
+        <v>0.19</v>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>0.23</v>
+        <v>0.096</v>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         </is>
       </c>
       <c r="F269" s="2" t="n">
-        <v>0.4</v>
+        <v>0.344</v>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         </is>
       </c>
       <c r="F270" s="2" t="n">
-        <v>0.081</v>
+        <v>0.174</v>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         </is>
       </c>
       <c r="F271" s="2" t="n">
-        <v>0.328</v>
+        <v>0.401</v>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         </is>
       </c>
       <c r="F272" s="2" t="n">
-        <v>0.271</v>
+        <v>0.205</v>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         </is>
       </c>
       <c r="F273" s="2" t="n">
-        <v>0.297</v>
+        <v>0.23</v>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         </is>
       </c>
       <c r="F274" s="2" t="n">
-        <v>0.308</v>
+        <v>0.287</v>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         </is>
       </c>
       <c r="F275" s="2" t="n">
-        <v>0.353</v>
+        <v>0.281</v>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>0.164</v>
+        <v>0.347</v>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
@@ -14310,7 +14310,7 @@
         </is>
       </c>
       <c r="F277" s="2" t="n">
-        <v>0.244</v>
+        <v>0.334</v>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         </is>
       </c>
       <c r="F278" s="2" t="n">
-        <v>0.107</v>
+        <v>0.096</v>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         </is>
       </c>
       <c r="F279" s="2" t="n">
-        <v>0.267</v>
+        <v>0.173</v>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
@@ -14460,7 +14460,7 @@
         </is>
       </c>
       <c r="F280" s="2" t="n">
-        <v>0.235</v>
+        <v>0.177</v>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         </is>
       </c>
       <c r="F281" s="2" t="n">
-        <v>0.291</v>
+        <v>0.35</v>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
@@ -14560,7 +14560,7 @@
         </is>
       </c>
       <c r="F282" s="2" t="n">
-        <v>0.204</v>
+        <v>0.307</v>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         </is>
       </c>
       <c r="F283" s="2" t="n">
-        <v>0.276</v>
+        <v>0.146</v>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="F284" s="2" t="n">
-        <v>0.309</v>
+        <v>0.188</v>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>0.367</v>
+        <v>0.185</v>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>0.397</v>
+        <v>0.32</v>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>0.146</v>
+        <v>0.4</v>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>0.082</v>
+        <v>0.204</v>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>0.147</v>
+        <v>0.247</v>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         </is>
       </c>
       <c r="F290" s="2" t="n">
-        <v>0.292</v>
+        <v>0.119</v>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>0.146</v>
+        <v>0.295</v>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>0.372</v>
+        <v>0.341</v>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="F293" s="2" t="n">
-        <v>0.092</v>
+        <v>0.102</v>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         </is>
       </c>
       <c r="F295" s="2" t="n">
-        <v>0.221</v>
+        <v>0.241</v>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>0.145</v>
+        <v>0.272</v>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>0.256</v>
+        <v>0.274</v>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>0.303</v>
+        <v>0.405</v>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         </is>
       </c>
       <c r="F299" s="2" t="n">
-        <v>0.15</v>
+        <v>0.326</v>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>0.097</v>
+        <v>0.242</v>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>0.324</v>
+        <v>0.309</v>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.118</v>
+        <v>0.379</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.151</v>
+        <v>0.156</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.138</v>
+        <v>0.375</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.349</v>
+        <v>0.223</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.313</v>
+        <v>0.367</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.278</v>
+        <v>0.259</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.104</v>
+        <v>0.17</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.192</v>
+        <v>0.222</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.264</v>
+        <v>0.322</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.239</v>
+        <v>0.377</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.195</v>
+        <v>0.345</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -16176,7 +16176,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.213</v>
+        <v>0.303</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.368</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.309</v>
+        <v>0.415</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.149</v>
+        <v>0.28</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.162</v>
+        <v>0.383</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.164</v>
+        <v>0.094</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.319</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.396</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.408</v>
+        <v>0.407</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.264</v>
+        <v>0.405</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.245</v>
+        <v>0.096</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.154</v>
+        <v>0.29</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.378</v>
+        <v>0.143</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.386</v>
+        <v>0.121</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.261</v>
+        <v>0.154</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.358</v>
+        <v>0.264</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.14</v>
+        <v>0.412</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.219</v>
+        <v>0.345</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.201</v>
+        <v>0.203</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -17126,7 +17126,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.116</v>
+        <v>0.384</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.172</v>
+        <v>0.38</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.3</v>
+        <v>0.297</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.41</v>
+        <v>0.412</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.17</v>
+        <v>0.126</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.089</v>
+        <v>0.409</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.303</v>
+        <v>0.116</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.322</v>
+        <v>0.334</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.206</v>
+        <v>0.305</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.234</v>
+        <v>0.302</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -17626,7 +17626,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.106</v>
+        <v>0.264</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.411</v>
+        <v>0.32</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.238</v>
+        <v>0.366</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.189</v>
+        <v>0.137</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.325</v>
+        <v>0.373</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.124</v>
+        <v>0.188</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.124</v>
+        <v>0.236</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.188</v>
+        <v>0.241</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.147</v>
+        <v>0.131</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.307</v>
+        <v>0.262</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.297</v>
+        <v>0.315</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.223</v>
+        <v>0.282</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.313</v>
+        <v>0.233</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.229</v>
+        <v>0.277</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.42</v>
+        <v>0.325</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.183</v>
+        <v>0.287</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.174</v>
+        <v>0.189</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.336</v>
+        <v>0.267</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.262</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.284</v>
+        <v>0.344</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.4</v>
+        <v>0.388</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.155</v>
+        <v>0.357</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.154</v>
+        <v>0.219</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.406</v>
+        <v>0.125</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.188</v>
+        <v>0.351</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.327</v>
+        <v>0.118</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.096</v>
+        <v>0.384</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.345</v>
+        <v>0.377</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.115</v>
+        <v>0.138</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.297</v>
+        <v>0.243</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.347</v>
+        <v>0.268</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -19176,7 +19176,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.206</v>
+        <v>0.41</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.324</v>
+        <v>0.406</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.242</v>
+        <v>0.365</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.29</v>
+        <v>0.323</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.158</v>
+        <v>0.292</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.335</v>
+        <v>0.113</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0.245</v>
+        <v>0.235</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0.186</v>
+        <v>0.11</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0.188</v>
+        <v>0.167</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -19626,7 +19626,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.112</v>
+        <v>0.387</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.224</v>
+        <v>0.313</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.132</v>
+        <v>0.18</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0.288</v>
+        <v>0.337</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.244</v>
+        <v>0.142</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0.273</v>
+        <v>0.229</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0.395</v>
+        <v>0.394</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.411</v>
+        <v>0.248</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0.396</v>
+        <v>0.145</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0.304</v>
+        <v>0.376</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -20126,7 +20126,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0.216</v>
+        <v>0.276</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0.345</v>
+        <v>0.33</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.081</v>
+        <v>0.311</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0.419</v>
+        <v>0.137</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.294</v>
+        <v>0.168</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0.214</v>
+        <v>0.254</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.277</v>
+        <v>0.396</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -20476,7 +20476,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0.29</v>
+        <v>0.359</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.369</v>
+        <v>0.244</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.109</v>
+        <v>0.153</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0.235</v>
+        <v>0.232</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0.109</v>
+        <v>0.192</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0.108</v>
+        <v>0.273</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0.415</v>
+        <v>0.224</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0.329</v>
+        <v>0.36</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.288</v>
+        <v>0.188</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.133</v>
+        <v>0.214</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0.347</v>
+        <v>0.08</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0.368</v>
+        <v>0.303</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0.232</v>
+        <v>0.391</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0.254</v>
+        <v>0.122</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0.296</v>
+        <v>0.319</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0.136</v>
+        <v>0.139</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0.383</v>
+        <v>0.381</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0.195</v>
+        <v>0.134</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0.366</v>
+        <v>0.096</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0.287</v>
+        <v>0.222</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0.231</v>
+        <v>0.33</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0.258</v>
+        <v>0.125</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0.318</v>
+        <v>0.126</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0.104</v>
+        <v>0.391</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0.259</v>
+        <v>0.14</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0.275</v>
+        <v>0.374</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>0.191</v>
+        <v>0.143</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>0.361</v>
+        <v>0.096</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0.233</v>
+        <v>0.277</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0.108</v>
+        <v>0.329</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>0.118</v>
+        <v>0.095</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0.298</v>
+        <v>0.219</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>0.105</v>
+        <v>0.394</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.234</v>
+        <v>0.398</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0.269</v>
+        <v>0.095</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0.41</v>
+        <v>0.083</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0.347</v>
+        <v>0.242</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0.112</v>
+        <v>0.265</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -22476,7 +22476,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0.217</v>
+        <v>0.254</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0.148</v>
+        <v>0.239</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0.252</v>
+        <v>0.204</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0.175</v>
+        <v>0.255</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0.094</v>
+        <v>0.137</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0.328</v>
+        <v>0.181</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0.304</v>
+        <v>0.38</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0.166</v>
+        <v>0.313</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>0.301</v>
+        <v>0.143</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0.198</v>
+        <v>0.095</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0.323</v>
+        <v>0.325</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -23026,7 +23026,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0.209</v>
+        <v>0.39</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0.302</v>
+        <v>0.125</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>0.247</v>
+        <v>0.33</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>0.416</v>
+        <v>0.401</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>0.201</v>
+        <v>0.27</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>0.381</v>
+        <v>0.292</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0.19</v>
+        <v>0.258</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0.188</v>
+        <v>0.237</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0.105</v>
+        <v>0.366</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0.205</v>
+        <v>0.36</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         </is>
       </c>
       <c r="F161" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>0.177</v>
+        <v>0.291</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -23676,7 +23676,7 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0.262</v>
+        <v>0.172</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0.381</v>
+        <v>0.082</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0.202</v>
+        <v>0.173</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -23826,7 +23826,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0.159</v>
+        <v>0.257</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>0.258</v>
+        <v>0.153</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>0.354</v>
+        <v>0.375</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>0.401</v>
+        <v>0.313</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>0.237</v>
+        <v>0.159</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -24076,7 +24076,7 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>0.235</v>
+        <v>0.332</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>0.167</v>
+        <v>0.095</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0.121</v>
+        <v>0.135</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>0.131</v>
+        <v>0.213</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>0.155</v>
+        <v>0.304</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>0.227</v>
+        <v>0.251</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>0.147</v>
+        <v>0.258</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>0.162</v>
+        <v>0.211</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>0.356</v>
+        <v>0.157</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>0.14</v>
+        <v>0.397</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>0.089</v>
+        <v>0.341</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>0.313</v>
+        <v>0.4</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>0.185</v>
+        <v>0.223</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>0.349</v>
+        <v>0.31</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -24826,7 +24826,7 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>0.3</v>
+        <v>0.226</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>0.307</v>
+        <v>0.359</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>0.386</v>
+        <v>0.309</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>0.239</v>
+        <v>0.201</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>0.398</v>
+        <v>0.252</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>0.242</v>
+        <v>0.095</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>0.222</v>
+        <v>0.184</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>0.371</v>
+        <v>0.305</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -25226,7 +25226,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>0.355</v>
+        <v>0.346</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0.369</v>
+        <v>0.154</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>0.272</v>
+        <v>0.302</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>0.099</v>
+        <v>0.399</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>0.137</v>
+        <v>0.322</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>0.322</v>
+        <v>0.24</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>0.298</v>
+        <v>0.115</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>0.114</v>
+        <v>0.385</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>0.237</v>
+        <v>0.098</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -25676,7 +25676,7 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>0.083</v>
+        <v>0.231</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>0.175</v>
+        <v>0.115</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>0.127</v>
+        <v>0.301</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>0.411</v>
+        <v>0.192</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>0.14</v>
+        <v>0.163</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>0.401</v>
+        <v>0.189</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>0.153</v>
+        <v>0.221</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>0.081</v>
+        <v>0.17</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>0.419</v>
+        <v>0.213</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>0.116</v>
+        <v>0.159</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -26176,7 +26176,7 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>0.363</v>
+        <v>0.299</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>0.41</v>
+        <v>0.13</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>0.125</v>
+        <v>0.319</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>0.148</v>
+        <v>0.317</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>0.153</v>
+        <v>0.209</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>0.225</v>
+        <v>0.407</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>0.116</v>
+        <v>0.113</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -26576,7 +26576,7 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>0.267</v>
+        <v>0.361</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>0.08</v>
+        <v>0.402</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>0.371</v>
+        <v>0.15</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>0.165</v>
+        <v>0.26</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>0.274</v>
+        <v>0.25</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -26826,7 +26826,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>0.126</v>
+        <v>0.19</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>0.418</v>
+        <v>0.153</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>0.217</v>
+        <v>0.378</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>0.31</v>
+        <v>0.233</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>0.242</v>
+        <v>0.28</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>0.167</v>
+        <v>0.255</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>0.116</v>
+        <v>0.305</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>0.296</v>
+        <v>0.335</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>0.418</v>
+        <v>0.337</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>0.14</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -27426,7 +27426,7 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>0.36</v>
+        <v>0.232</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>0.178</v>
+        <v>0.383</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         </is>
       </c>
       <c r="F240" t="n">
-        <v>0.211</v>
+        <v>0.357</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>0.222</v>
+        <v>0.251</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>0.115</v>
+        <v>0.093</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>0.329</v>
+        <v>0.107</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>0.415</v>
+        <v>0.377</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>0.191</v>
+        <v>0.146</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>0.171</v>
+        <v>0.335</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>0.149</v>
+        <v>0.249</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>0.332</v>
+        <v>0.292</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>0.285</v>
+        <v>0.352</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>0.116</v>
+        <v>0.262</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>0.116</v>
+        <v>0.225</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -28176,7 +28176,7 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>0.104</v>
+        <v>0.366</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         </is>
       </c>
       <c r="F254" t="n">
-        <v>0.335</v>
+        <v>0.395</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         </is>
       </c>
       <c r="F255" t="n">
-        <v>0.415</v>
+        <v>0.117</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         </is>
       </c>
       <c r="F256" t="n">
-        <v>0.414</v>
+        <v>0.12</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>0.378</v>
+        <v>0.136</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>0.329</v>
+        <v>0.26</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>0.167</v>
+        <v>0.165</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>0.214</v>
+        <v>0.309</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>0.271</v>
+        <v>0.293</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>0.143</v>
+        <v>0.309</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -28676,7 +28676,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>0.165</v>
+        <v>0.323</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>0.351</v>
+        <v>0.216</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>0.091</v>
+        <v>0.218</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>0.273</v>
+        <v>0.19</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -28926,7 +28926,7 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>0.23</v>
+        <v>0.096</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>0.4</v>
+        <v>0.344</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -29026,7 +29026,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>0.081</v>
+        <v>0.174</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>0.328</v>
+        <v>0.401</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -29126,7 +29126,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>0.271</v>
+        <v>0.205</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>0.297</v>
+        <v>0.23</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>0.308</v>
+        <v>0.287</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>0.353</v>
+        <v>0.281</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>0.164</v>
+        <v>0.347</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>0.244</v>
+        <v>0.334</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>0.107</v>
+        <v>0.096</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>0.267</v>
+        <v>0.173</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -29526,7 +29526,7 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>0.235</v>
+        <v>0.177</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>0.291</v>
+        <v>0.35</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -29626,7 +29626,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>0.204</v>
+        <v>0.307</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>0.276</v>
+        <v>0.146</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>0.309</v>
+        <v>0.188</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>0.367</v>
+        <v>0.185</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>0.397</v>
+        <v>0.32</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
@@ -29876,7 +29876,7 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>0.146</v>
+        <v>0.4</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>0.082</v>
+        <v>0.204</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>0.147</v>
+        <v>0.247</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
@@ -30026,7 +30026,7 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>0.292</v>
+        <v>0.119</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>0.146</v>
+        <v>0.295</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
@@ -30126,7 +30126,7 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>0.372</v>
+        <v>0.341</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
@@ -30176,7 +30176,7 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>0.092</v>
+        <v>0.102</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>0.221</v>
+        <v>0.241</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>0.145</v>
+        <v>0.272</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         </is>
       </c>
       <c r="F297" t="n">
-        <v>0.256</v>
+        <v>0.274</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         </is>
       </c>
       <c r="F298" t="n">
-        <v>0.303</v>
+        <v>0.405</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
@@ -30476,7 +30476,7 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>0.15</v>
+        <v>0.326</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>0.097</v>
+        <v>0.242</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>0.324</v>
+        <v>0.309</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72.92</v>
+        <v>76.73</v>
       </c>
     </row>
     <row r="10">
@@ -30851,7 +30851,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-12 11:08:42</t>
+          <t>2026-08-19 09:31:15</t>
         </is>
       </c>
     </row>
